--- a/artfynd/A 45454-2025 artfynd.xlsx
+++ b/artfynd/A 45454-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86375817</v>
+        <v>89045278</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ö Sörviken, Jmt</t>
+          <t>Rismyren, 500 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547670.0042832248</v>
+        <v>547873</v>
       </c>
       <c r="R2" t="n">
-        <v>7046962.145035216</v>
+        <v>7046874</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,22 +754,139 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gammal odikad gransumpskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # skrymsle vid basen av björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>86375817</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ö Sörviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>547670</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7046962</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-05-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 45454-2025 artfynd.xlsx
+++ b/artfynd/A 45454-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89045278</t>
         </is>
       </c>
     </row>
@@ -891,8 +901,17 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86375817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>